--- a/Deliverables/GC EA assessment tool - categories.xlsx
+++ b/Deliverables/GC EA assessment tool - categories.xlsx
@@ -760,7 +760,7 @@
     <row r="4" ht="22.4" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>The one thing we are asking for</t>
+          <t>What we are asking you for</t>
         </is>
       </c>
     </row>
@@ -812,21 +812,21 @@
     <row r="14" ht="22.4" customHeight="1">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>The nine categories</t>
+          <t>The five you fill in</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Four are the domains themselves, filled in by the tab a question is on: Business, Data, Application, Technology.</t>
+          <t>Security, Privacy, Financial, Accessibility, Official Languages. Those are the whole of the Categories column.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Five are what the Categories column asks for: Security, Privacy, Financial, Accessibility, Official Languages.</t>
+          <t>Business, Data, Application and Technology are categories too, and you never type them: a question carries the one its own tab is named after, automatically.</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
     <row r="20" ht="22.4" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Never duplicate a question onto a second tab</t>
+          <t>Never put a question in two domains</t>
         </is>
       </c>
     </row>
